--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260223_203324.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260223_203324.xlsx
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260223_203324.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260223_203324.xlsx
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
